--- a/artfynd/A 30000-2026 artfynd.xlsx
+++ b/artfynd/A 30000-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92179437</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,8 +888,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125667855</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30000-2026 artfynd.xlsx
+++ b/artfynd/A 30000-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,50 +680,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92179437</v>
+        <v>136477165</v>
       </c>
       <c r="B2" t="n">
-        <v>104627</v>
+        <v>61562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>106670</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart skogssnigel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Arion ater ater</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hylta Brostugan, Östra Göinge, Sk</t>
+          <t>Hylta, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450560</v>
+        <v>450416</v>
       </c>
       <c r="R2" t="n">
-        <v>6232736</v>
+        <v>6232721</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,12 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-04-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-04-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,72 +764,76 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kalle Lindberg</t>
+          <t>Carl-Axel Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kalle Lindberg</t>
+          <t>Carl-Axel Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92179437</t>
+          <t>https://artportalen.se/Sighting/136477165</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125667855</v>
+        <v>92179437</v>
       </c>
       <c r="B3" t="n">
-        <v>103403</v>
+        <v>104627</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>223246</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hylta, Sk</t>
+          <t>Hylta Brostugan, Östra Göinge, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450448</v>
+        <v>450560</v>
       </c>
       <c r="R3" t="n">
-        <v>6232746</v>
+        <v>6232736</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -853,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2021-04-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2021-04-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,28 +874,134 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>vägren</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carl-Axel Andersson</t>
+          <t>Kalle Lindberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl-Axel Andersson</t>
+          <t>Kalle Lindberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92179437</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125667855</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hylta, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>450448</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6232746</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östra Göinge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hjärsås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>vägren</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Carl-Axel Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Carl-Axel Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125667855</t>
         </is>
@@ -898,6 +1011,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
